--- a/键值对应开关.xlsx
+++ b/键值对应开关.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\esphome\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA26CA2-0EC1-4185-A34B-C8C64B85601B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE76F0C5-B8D8-491C-9C0C-4C5ABE9E9431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="5400" windowWidth="23040" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>遥控器a按键1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -372,6 +372,119 @@
   </si>
   <si>
     <t>011010100100100100010100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000001100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000110000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011001100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011001111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000111100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遥控器c按键1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遥控器c按键2</t>
+  </si>
+  <si>
+    <t>遥控器c按键3</t>
+  </si>
+  <si>
+    <t>遥控器c按键4</t>
+  </si>
+  <si>
+    <t>遥控器c按键5</t>
+  </si>
+  <si>
+    <t>遥控器c按键6</t>
+  </si>
+  <si>
+    <t>遥控器c按键7</t>
+  </si>
+  <si>
+    <t>遥控器c按键8</t>
+  </si>
+  <si>
+    <t>遥控器c按键9</t>
+  </si>
+  <si>
+    <t>遥控器c按键10</t>
+  </si>
+  <si>
+    <t>遥控器c按键11</t>
+  </si>
+  <si>
+    <t>遥控器c按键12</t>
+  </si>
+  <si>
+    <t>遥控器c按键13</t>
+  </si>
+  <si>
+    <t>遥控器c按键14</t>
+  </si>
+  <si>
+    <t>遥控器c按键15</t>
+  </si>
+  <si>
+    <t>遥控器c按键16</t>
+  </si>
+  <si>
+    <t>010101010101010000111111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011110000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000001111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011111100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011110011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011111111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010011000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000110011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010101010101010000000000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -713,6 +826,8 @@
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -728,8 +843,12 @@
       <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -744,8 +863,12 @@
       <c r="D2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -760,8 +883,12 @@
       <c r="D3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -776,8 +903,12 @@
       <c r="D4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -792,8 +923,12 @@
       <c r="D5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -808,8 +943,12 @@
       <c r="D6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -824,8 +963,12 @@
       <c r="D7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -840,8 +983,12 @@
       <c r="D8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -856,8 +1003,12 @@
       <c r="D9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -872,8 +1023,12 @@
       <c r="D10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -888,8 +1043,12 @@
       <c r="D11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -904,8 +1063,12 @@
       <c r="D12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -920,8 +1083,12 @@
       <c r="D13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -936,8 +1103,12 @@
       <c r="D14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -952,8 +1123,12 @@
       <c r="D15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -968,8 +1143,12 @@
       <c r="D16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
